--- a/老余裸K圖表_20260610/老余裸K_賺賠比精選_20260610.xlsx
+++ b/老余裸K圖表_20260610/老余裸K_賺賠比精選_20260610.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -584,33 +584,33 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>4714.TWO</t>
+          <t>4564.TW</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>永捷</t>
+          <t>元翎</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>1 : 5.27</t>
+          <t>1 : 9.64</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>13.5</v>
+        <v>15.15</v>
       </c>
       <c r="E3" s="9" t="n">
-        <v>12.75</v>
+        <v>14.6</v>
       </c>
       <c r="F3" s="9" t="n">
-        <v>17.45</v>
+        <v>20.45</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>0.75</v>
+        <v>0.55</v>
       </c>
       <c r="H3" s="10" t="n">
-        <v>1840</v>
+        <v>919</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -621,33 +621,33 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>8034.TWO</t>
+          <t>2208.TW</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>台船</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>1 : 4.24</t>
+          <t>1 : 6.23</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>23.4</v>
+        <v>17.85</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>22.55</v>
+        <v>17.2</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>27</v>
+        <v>21.9</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>518</v>
+        <v>2631</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -658,33 +658,33 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>4123.TWO</t>
+          <t>4714.TWO</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>永捷</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>1 : 3.73</t>
+          <t>1 : 5.27</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>37.95</v>
+        <v>13.5</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>36.85</v>
+        <v>12.75</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>42.05</v>
+        <v>17.45</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>2155</v>
+        <v>1840</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
@@ -695,33 +695,33 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>7717.TWO</t>
+          <t>4560.TW</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>強信-KY</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1 : 2.77</t>
+          <t>1 : 4.59</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>654</v>
+        <v>32.45</v>
       </c>
       <c r="E6" s="4" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>544</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>959</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>677</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -732,35 +732,405 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
+          <t>8034.TWO</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>榮群</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>1 : 4.24</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>518</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>5258.TW</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>虹堡</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>1 : 4.22</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>610</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>4123.TWO</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>晟德</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>1 : 3.73</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>2155</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2548.TW</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>華固</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>1 : 3.06</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>123.85</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>8421</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>4119.TW</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>旭富</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>1 : 2.91</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>719</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>7717.TWO</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>萊德光電-KY</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>1 : 2.77</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>654</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>544</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>959</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>677</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>1736.TW</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>喬山</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>1 : 2.75</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>112</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>1182</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>4745.TWO</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>合富-KY</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>1 : 2.69</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D14" s="4" t="n">
         <v>16.5</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E14" s="4" t="n">
         <v>15.05</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F14" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G14" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="H7" s="10" t="n">
+      <c r="H14" s="5" t="n">
         <v>1248</v>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>4934.TW</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>太極</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>1 : 2.63</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>1904</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>1225.TW</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>福懋油</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>1 : 2.4</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>527</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>點我查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>1795.TW</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>美時</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>1 : 2.0</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>202</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>182</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>242</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>2502</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -774,6 +1144,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/老余裸K圖表_20260610/老余裸K_賺賠比精選_20260610.xlsx
+++ b/老余裸K圖表_20260610/老余裸K_賺賠比精選_20260610.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -732,33 +732,33 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>8034.TWO</t>
+          <t>5258.TW</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>虹堡</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>1 : 4.24</t>
+          <t>1 : 4.22</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>23.4</v>
+        <v>48.85</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>22.55</v>
+        <v>45.5</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0.85</v>
+        <v>3.35</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>518</v>
+        <v>610</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -769,33 +769,33 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5258.TW</t>
+          <t>4123.TWO</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>虹堡</t>
+          <t>晟德</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1 : 4.22</t>
+          <t>1 : 3.73</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>48.85</v>
+        <v>37.95</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>45.5</v>
+        <v>36.85</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>63</v>
+        <v>42.05</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>3.35</v>
+        <v>1.1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>610</v>
+        <v>2155</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -806,33 +806,33 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>4123.TWO</t>
+          <t>2548.TW</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>晟德</t>
+          <t>華固</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>1 : 3.73</t>
+          <t>1 : 3.06</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>37.95</v>
+        <v>105.5</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>36.85</v>
+        <v>99.5</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>42.05</v>
+        <v>123.85</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="H9" s="10" t="n">
-        <v>2155</v>
+        <v>8421</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -843,33 +843,33 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>2548.TW</t>
+          <t>4119.TW</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>華固</t>
+          <t>旭富</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>1 : 3.06</t>
+          <t>1 : 2.91</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>105.5</v>
+        <v>42.95</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>99.5</v>
+        <v>39.6</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>123.85</v>
+        <v>52.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>8421</v>
+        <v>719</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -880,33 +880,33 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>4119.TW</t>
+          <t>6156.TWO</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>旭富</t>
+          <t>松上</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>1 : 2.91</t>
+          <t>1 : 2.85</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>42.95</v>
+        <v>18.85</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>39.6</v>
+        <v>17.85</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>52.7</v>
+        <v>21.7</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>3.35</v>
+        <v>1</v>
       </c>
       <c r="H11" s="10" t="n">
-        <v>719</v>
+        <v>538</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -917,33 +917,33 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>7717.TWO</t>
+          <t>1736.TW</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>喬山</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>1 : 2.77</t>
+          <t>1 : 2.75</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>654</v>
+        <v>112</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>544</v>
+        <v>102</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>959</v>
+        <v>139.5</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>110</v>
+        <v>10</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>677</v>
+        <v>1182</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -954,33 +954,33 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>1736.TW</t>
+          <t>4745.TWO</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>喬山</t>
+          <t>合富-KY</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>1 : 2.75</t>
+          <t>1 : 2.69</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>112</v>
+        <v>16.5</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>102</v>
+        <v>15.05</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>139.5</v>
+        <v>20.4</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>10</v>
+        <v>1.45</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>1182</v>
+        <v>1248</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
@@ -991,33 +991,33 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>4745.TWO</t>
+          <t>4934.TW</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>合富-KY</t>
+          <t>太極</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>1 : 2.69</t>
+          <t>1 : 2.63</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>16.5</v>
+        <v>16.25</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>15.05</v>
+        <v>14.9</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>20.4</v>
+        <v>19.8</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>1248</v>
+        <v>1904</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1028,33 +1028,33 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>4934.TW</t>
+          <t>1225.TW</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>太極</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>1 : 2.63</t>
+          <t>1 : 2.4</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>16.25</v>
+        <v>30.35</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>14.9</v>
+        <v>28.6</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>19.8</v>
+        <v>34.55</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>1904</v>
+        <v>527</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
@@ -1065,72 +1065,35 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>1225.TW</t>
+          <t>1795.TW</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>美時</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>1 : 2.4</t>
+          <t>1 : 2.0</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>30.35</v>
+        <v>202</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>28.6</v>
+        <v>182</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>34.55</v>
+        <v>242</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.75</v>
+        <v>20</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>527</v>
+        <v>2502</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>1795.TW</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>美時</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>1 : 2.0</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>202</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>182</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>242</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>2502</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -1153,7 +1116,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
